--- a/Laboratory Alumni Information Collection Form  (Responses).xlsx
+++ b/Laboratory Alumni Information Collection Form  (Responses).xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>Timestamp</t>
   </si>
@@ -270,6 +270,63 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=12uuz5svTpBVqpc284c7F3AmjQIxwpVPk</t>
+  </si>
+  <si>
+    <t>8/23/2026 21:58:45</t>
+  </si>
+  <si>
+    <t>Rajib Kumar Shil</t>
+  </si>
+  <si>
+    <t>rajibbmb@cu.ac.bd</t>
+  </si>
+  <si>
+    <t>2005-2006</t>
+  </si>
+  <si>
+    <t>2010 (Held in 2012)</t>
+  </si>
+  <si>
+    <t>Herbert Wertheim College of Medicine, FIU, Miami, FL, US</t>
+  </si>
+  <si>
+    <t>PhD Candidate</t>
+  </si>
+  <si>
+    <t>Isolation of Potential Cellulolytic Microorganisms from the gut of three different Insect species</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=i1i9gxYAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
+  </si>
+  <si>
+    <t>This lab shaped me as a researcher I am today.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1d33M_ASctWjW4BYoyDcmCQWagyV94DPO</t>
+  </si>
+  <si>
+    <t>8/23/2026 22:29:53</t>
+  </si>
+  <si>
+    <t>Bristy Barua</t>
+  </si>
+  <si>
+    <t>bristybmb@gmail.com</t>
+  </si>
+  <si>
+    <t>2009-2010</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>Effects of extraction solvents on the phenolic content and antioxidant activity of Bangladeshi wild date fruit (Phoenix Sylvestris Roxb)</t>
+  </si>
+  <si>
+    <t>As I wrap up my time here, I would like to thank this incredible team for the shared discoveries, resilience, and curiosity that made our lab feel like home. Keep pushing the boundaries of research with same dedication and achieving all breakthroughs.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ktlRbWIgP-4YkYKryZvu3Q-R1bMRcmqq</t>
   </si>
 </sst>
 </file>
@@ -423,21 +480,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M8" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" displayName="Form_Responses" id="1" name="Form_Responses" ref="A1:M10">
   <tableColumns count="13">
-    <tableColumn name="Timestamp" id="1"/>
-    <tableColumn name="Full Name " id="2"/>
-    <tableColumn name="Email " id="3"/>
-    <tableColumn name="Academic Session" id="4"/>
-    <tableColumn name="Year of MS Completion" id="5"/>
-    <tableColumn name="Present Workplace / Organization / Institution" id="6"/>
-    <tableColumn name="Current Position/Designation" id="7"/>
-    <tableColumn name="Research Topic/Thesis Title During Your Time in the Lab  " id="8"/>
-    <tableColumn name="Google Scholar Profile URL" id="9"/>
-    <tableColumn name="ResearchGate Profile URL" id="10"/>
-    <tableColumn name="ORCID ID" id="11"/>
-    <tableColumn name="Share your experience, memories, or a short message about your time in the laboratory (within 120 words)" id="12"/>
-    <tableColumn name="Profile Photo (for website display)" id="13"/>
+    <tableColumn id="1" name="Timestamp"/>
+    <tableColumn id="2" name="Full Name "/>
+    <tableColumn id="3" name="Email "/>
+    <tableColumn id="4" name="Academic Session"/>
+    <tableColumn id="5" name="Year of MS Completion"/>
+    <tableColumn id="6" name="Present Workplace / Organization / Institution"/>
+    <tableColumn id="7" name="Current Position/Designation"/>
+    <tableColumn id="8" name="Research Topic/Thesis Title During Your Time in the Lab  "/>
+    <tableColumn id="9" name="Google Scholar Profile URL"/>
+    <tableColumn id="10" name="ResearchGate Profile URL"/>
+    <tableColumn id="11" name="ORCID ID"/>
+    <tableColumn id="12" name="Share your experience, memories, or a short message about your time in the laboratory (within 120 words)"/>
+    <tableColumn id="13" name="Profile Photo (for website display)"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -638,26 +695,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="18.88"/>
-    <col customWidth="1" min="5" max="5" width="25.63"/>
-    <col customWidth="1" min="6" max="6" width="37.63"/>
-    <col customWidth="1" min="7" max="7" width="26.38"/>
-    <col customWidth="1" min="8" max="8" width="37.63"/>
-    <col customWidth="1" min="9" max="9" width="24.88"/>
-    <col customWidth="1" min="10" max="10" width="24.0"/>
-    <col customWidth="1" min="11" max="11" width="18.88"/>
-    <col customWidth="1" min="12" max="12" width="37.63"/>
-    <col customWidth="1" min="13" max="13" width="61.38"/>
-    <col customWidth="1" min="14" max="19" width="18.88"/>
+    <col customWidth="1" max="4" min="1" width="18.88"/>
+    <col customWidth="1" max="5" min="5" width="25.63"/>
+    <col customWidth="1" max="6" min="6" width="37.63"/>
+    <col customWidth="1" max="7" min="7" width="26.38"/>
+    <col customWidth="1" max="8" min="8" width="37.63"/>
+    <col customWidth="1" max="9" min="9" width="24.88"/>
+    <col customWidth="1" max="10" min="10" width="24.0"/>
+    <col customWidth="1" max="11" min="11" width="18.88"/>
+    <col customWidth="1" max="12" min="12" width="37.63"/>
+    <col customWidth="1" max="13" min="13" width="61.38"/>
+    <col customWidth="1" max="19" min="14" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,7 +755,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="2">
       <c r="A2" s="2">
         <v>46241.345694247684</v>
       </c>
@@ -729,7 +786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="3">
       <c r="A3" s="6">
         <v>46252.83406586805</v>
       </c>
@@ -764,7 +821,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="4">
       <c r="A4" s="6">
         <v>46253.07958832176</v>
       </c>
@@ -802,7 +859,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="5">
       <c r="A5" s="6">
         <v>46254.38134586805</v>
       </c>
@@ -843,7 +900,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="6">
       <c r="A6" s="6">
         <v>46255.04038869213</v>
       </c>
@@ -878,7 +935,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="7">
       <c r="A7" s="6">
         <v>46256.817238993055</v>
       </c>
@@ -919,7 +976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row customHeight="1" ht="22.5" r="8">
       <c r="A8" s="6">
         <v>46257.56692534722</v>
       </c>
@@ -958,34 +1015,95 @@
       </c>
       <c r="M8" s="8" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="22.5" r="9">
+      <c r="A9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="22.5" r="10">
+      <c r="A10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="M2"/>
-    <hyperlink r:id="rId3" ref="M3"/>
-    <hyperlink r:id="rId4" ref="I4"/>
-    <hyperlink r:id="rId5" ref="J4"/>
-    <hyperlink r:id="rId6" ref="K4"/>
-    <hyperlink r:id="rId7" ref="M4"/>
-    <hyperlink r:id="rId8" ref="I5"/>
-    <hyperlink r:id="rId9" ref="J5"/>
-    <hyperlink r:id="rId10" ref="K5"/>
-    <hyperlink r:id="rId11" ref="M5"/>
-    <hyperlink r:id="rId12" ref="I6"/>
-    <hyperlink r:id="rId13" ref="M6"/>
-    <hyperlink r:id="rId14" ref="I7"/>
-    <hyperlink r:id="rId15" ref="J7"/>
-    <hyperlink r:id="rId16" ref="M7"/>
-    <hyperlink r:id="rId17" ref="I8"/>
-    <hyperlink r:id="rId18" ref="J8"/>
-    <hyperlink r:id="rId19" ref="K8"/>
-    <hyperlink r:id="rId20" ref="M8"/>
+    <hyperlink ref="M2" ns1:id="rId2"/>
+    <hyperlink ref="M3" ns1:id="rId3"/>
+    <hyperlink ref="I4" ns1:id="rId4"/>
+    <hyperlink ref="J4" ns1:id="rId5"/>
+    <hyperlink ref="K4" ns1:id="rId6"/>
+    <hyperlink ref="M4" ns1:id="rId7"/>
+    <hyperlink ref="I5" ns1:id="rId8"/>
+    <hyperlink ref="J5" ns1:id="rId9"/>
+    <hyperlink ref="K5" ns1:id="rId10"/>
+    <hyperlink ref="M5" ns1:id="rId11"/>
+    <hyperlink ref="I6" ns1:id="rId12"/>
+    <hyperlink ref="M6" ns1:id="rId13"/>
+    <hyperlink ref="I7" ns1:id="rId14"/>
+    <hyperlink ref="J7" ns1:id="rId15"/>
+    <hyperlink ref="M7" ns1:id="rId16"/>
+    <hyperlink ref="I8" ns1:id="rId17"/>
+    <hyperlink ref="J8" ns1:id="rId18"/>
+    <hyperlink ref="K8" ns1:id="rId19"/>
+    <hyperlink ref="M8" ns1:id="rId20"/>
   </hyperlinks>
-  <drawing r:id="rId21"/>
-  <legacyDrawing r:id="rId22"/>
+  <drawing ns1:id="rId21"/>
+  <legacyDrawing ns1:id="rId22"/>
   <tableParts count="1">
-    <tablePart r:id="rId24"/>
+    <tablePart ns1:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>